--- a/Bancos_carteras_propias.xlsx
+++ b/Bancos_carteras_propias.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BEF9A38-73F5-A04E-87E6-4010CDBF0419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D215119-F303-3E47-BCF0-AE80F7204325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15980" xr2:uid="{73D4B19A-438F-4062-9AF9-967B30BBDBA1}"/>
+    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="15980" xr2:uid="{73D4B19A-438F-4062-9AF9-967B30BBDBA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -52,9 +52,6 @@
     <t>BANCO AV VILLAS 9784 CONTACTO</t>
   </si>
   <si>
-    <t>BANCO AV VILLAS 2846 CONTACTO</t>
-  </si>
-  <si>
     <t>Efecty 24345 PA FTP NOVARTEC SAS</t>
   </si>
   <si>
@@ -83,6 +80,9 @@
   </si>
   <si>
     <t>BANCOLOMBIA 0934 NOVARTEC o convenio 31011</t>
+  </si>
+  <si>
+    <t>BANCO AV VILLAS 2846 CONTACTO o Convenio 28011</t>
   </si>
 </sst>
 </file>
@@ -490,22 +490,22 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -515,7 +515,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -525,7 +525,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -535,12 +535,12 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -550,7 +550,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E13" s="2"/>
     </row>
@@ -561,13 +561,13 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" s="2"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
